--- a/outputs/daily/hr_rankings_2026-07-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-19.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -788,11 +788,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>67.8</v>
+        <v>60.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -806,65 +818,61 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>82.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R2" t="n">
         <v>60.7</v>
       </c>
       <c r="S2" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>74.5</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -901,7 +909,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -974,15 +982,39 @@
           <t>0.2798</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1048,7 +1080,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1072,11 +1104,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59.7</v>
+        <v>60.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1086,7 +1118,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1099,7 +1131,7 @@
         <v>60.7</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1109,39 +1141,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1286,7 +1314,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1327,24 +1355,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -1352,19 +1380,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>53.6</v>
+        <v>52.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1378,65 +1418,61 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>47</v>
+        <v>50.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>15.3</v>
       </c>
       <c r="R4" t="n">
         <v>60.7</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>15.3</v>
+        <v>57.8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1458,22 +1494,22 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1483,78 +1519,102 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.8553</t>
+          <t>101.1264</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4894</t>
+          <t>0.4679</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.2122</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>70.51</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1986</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+          <t>0.1975</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1620,7 +1680,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1628,11 +1688,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>53.3</v>
+        <v>48.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1646,65 +1718,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>38.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R5" t="n">
         <v>60.7</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U5" t="n">
         <v>54.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1741,7 +1809,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1814,15 +1882,39 @@
           <t>0.196</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -1863,12 +1955,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1888,12 +1980,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1912,7 +2004,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52.1</v>
+        <v>46.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1926,11 +2018,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.8</v>
+        <v>42.5</v>
       </c>
       <c r="Q6" t="n">
         <v>15.3</v>
@@ -1939,49 +2031,45 @@
         <v>60.7</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>57.8</v>
+        <v>34.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2006,17 +2094,17 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2031,67 +2119,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.1264</t>
+          <t>100.3793</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4679</t>
+          <t>0.3977</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2122</t>
+          <t>0.1805</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.3075</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.51</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>52.68</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.1907</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2126,7 +2214,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2167,12 +2255,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2192,19 +2280,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>49.5</v>
+        <v>46.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2218,65 +2318,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>39.2</v>
+        <v>47</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R7" t="n">
         <v>60.7</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2293,12 +2389,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2308,12 +2404,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2323,78 +2419,102 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.5962</t>
+          <t>100.8553</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3663</t>
+          <t>0.4894</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1528</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.2866</t>
+          <t>0.371</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>74.08</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1678</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1986</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2435,24 +2555,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>502671</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Paul Goldschmidt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -2460,19 +2580,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>48.3</v>
+        <v>44.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2486,65 +2618,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>33.8</v>
+        <v>39.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>15.3</v>
       </c>
       <c r="R8" t="n">
         <v>60.7</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8</v>
+        <v>18.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2566,103 +2694,127 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 3/25, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>98.5765</t>
+          <t>99.7145</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1917</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>71.69</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1697</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+          <t>0.2004</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -2703,12 +2855,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2728,19 +2880,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>47.8</v>
+        <v>44.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2754,65 +2918,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>45.5</v>
+        <v>57.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R9" t="n">
         <v>60.7</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2829,27 +2989,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2859,78 +3019,102 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.0294</t>
+          <t>101.4308</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.4963</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.2478</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3265</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1622</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+          <t>0.234</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -2971,24 +3155,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -2996,19 +3180,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>45.8</v>
+        <v>44.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3022,65 +3218,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>43.9</v>
+        <v>30.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.2</v>
+        <v>15.3</v>
       </c>
       <c r="R10" t="n">
         <v>60.7</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>4.5</v>
+        <v>26.4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3097,12 +3289,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3112,12 +3304,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3127,78 +3319,102 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.5901</t>
+          <t>98.5451</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4091</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1732</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>32.13</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1879</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+          <t>0.1779</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3239,24 +3455,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jazz Chisholm</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -3264,31 +3480,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>45.8</v>
+        <v>43.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3302,62 +3518,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>42.5</v>
+        <v>33.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="R11" t="n">
         <v>60.7</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U11" t="n">
-        <v>34.9</v>
+        <v>0.8</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3377,132 +3589,132 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>38.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.3793</t>
+          <t>98.5765</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3977</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1805</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3075</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>52.68</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1907</t>
+          <t>0.1697</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -3543,24 +3755,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>691176</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jasson Domínguez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -3568,19 +3780,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>45.6</v>
+        <v>43</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3594,65 +3818,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>33.3</v>
+        <v>28</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>15.2</v>
       </c>
       <c r="R12" t="n">
         <v>60.7</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>4.2</v>
+        <v>43.2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3669,27 +3889,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 0 HR</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3699,78 +3919,102 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.9121</t>
+          <t>100.8327</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4172</t>
+          <t>0.3791</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1521</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3461</t>
+          <t>0.3046</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>74.17</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1497</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.1632</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -3811,24 +4055,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>641857</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -3836,31 +4080,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>45.3</v>
+        <v>42.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3874,62 +4118,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>49.9</v>
+        <v>45.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="R13" t="n">
         <v>60.7</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3949,27 +4189,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3979,102 +4219,102 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>102.1951</t>
+          <t>101.0294</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4113</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1807</t>
+          <t>0.1864</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3122</t>
+          <t>0.3265</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>74.49</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1677</t>
+          <t>0.1622</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4115,12 +4355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>669224</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4140,12 +4380,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4164,7 +4404,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.9</v>
+        <v>41.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4178,11 +4418,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>30.2</v>
+        <v>36.7</v>
       </c>
       <c r="Q14" t="n">
         <v>15.3</v>
@@ -4191,49 +4431,45 @@
         <v>60.7</v>
       </c>
       <c r="S14" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>26.4</v>
+        <v>41.2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4253,22 +4489,22 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -4283,67 +4519,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.5451</t>
+          <t>100.623</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.3675</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.2877</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>46.73</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1365</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -4378,7 +4614,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4419,24 +4655,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>691176</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jasson Dominguez</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -4444,31 +4680,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>43.8</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4482,62 +4718,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>28</v>
+        <v>33.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.2</v>
+        <v>11.5</v>
       </c>
       <c r="R15" t="n">
         <v>60.7</v>
       </c>
       <c r="S15" t="n">
-        <v>92.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>43.2</v>
+        <v>4.2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4557,27 +4789,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4587,102 +4819,102 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.8327</t>
+          <t>98.9121</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3791</t>
+          <t>0.4172</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.1521</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3046</t>
+          <t>0.3461</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>21.08</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>44.08</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1632</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -4723,12 +4955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4748,19 +4980,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>38.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4774,65 +5018,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>27.4</v>
+        <v>21.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>40.2</v>
+        <v>11.5</v>
       </c>
       <c r="R16" t="n">
         <v>60.7</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>36</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4849,12 +5089,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4864,12 +5104,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4879,78 +5119,102 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.14</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.1334</t>
+          <t>98.4444</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.3979</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1265</t>
+          <t>0.1209</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.3161</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.55</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.07</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1472</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+          <t>0.1315</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -4991,12 +5255,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680474</t>
+          <t>683011</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Max Schuemann</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5016,12 +5280,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5040,7 +5304,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.4</v>
+        <v>34.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5054,11 +5318,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>33</v>
+        <v>21.9</v>
       </c>
       <c r="Q17" t="n">
         <v>15.3</v>
@@ -5067,49 +5331,45 @@
         <v>60.7</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>22</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed; order MLB 5 vs RotoWire 9</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5134,7 +5394,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5144,7 +5404,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 4/15, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5154,72 +5414,72 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.21</t>
+          <t>88.25</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.4682</t>
+          <t>98.8398</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3557</t>
+          <t>0.3427</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1411</t>
+          <t>0.1127</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2975</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.82</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1649</t>
+          <t>0.1097</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5254,7 +5514,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5295,24 +5555,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>683011</t>
+          <t>672613</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Eliezer Alfonzo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -5320,31 +5580,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34</v>
+        <v>29.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5358,65 +5618,61 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>21.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.3</v>
+        <v>10.8</v>
       </c>
       <c r="R18" t="n">
         <v>60.7</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5428,17 +5684,17 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5448,117 +5704,117 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 0 HR</t>
+          <t>Last 5 games: 0/9, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.8398</t>
+          <t>95.0081</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3427</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1127</t>
+          <t>0.044</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2975</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1097</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -5599,12 +5855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>645305</t>
+          <t>676609</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ali Sanchez</t>
+          <t>José Caballero</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5624,7 +5880,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5648,7 +5904,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.2</v>
+        <v>26.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5662,11 +5918,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q19" t="n">
         <v>15.3</v>
@@ -5675,49 +5931,45 @@
         <v>60.7</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>9.300000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5737,12 +5989,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5752,7 +6004,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/11, 0 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -5767,67 +6019,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.46</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>95.6331</t>
+          <t>96.3508</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.3306</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0847</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2776</t>
+          <t>0.2794</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>68.96</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0702</t>
+          <t>0.1348</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5862,7 +6114,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6274,7 +6526,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6282,11 +6534,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>67.8</v>
+        <v>60.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6300,65 +6564,61 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>82.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R2" t="n">
         <v>60.7</v>
       </c>
       <c r="S2" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>74.5</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -6395,7 +6655,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -6468,15 +6728,39 @@
           <t>0.2798</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -6542,7 +6826,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6566,11 +6850,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59.7</v>
+        <v>60.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6580,7 +6864,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6593,7 +6877,7 @@
         <v>60.7</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6603,39 +6887,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6780,7 +7060,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -6821,24 +7101,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -6846,19 +7126,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>53.6</v>
+        <v>52.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6872,65 +7164,61 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>47</v>
+        <v>50.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>15.3</v>
       </c>
       <c r="R4" t="n">
         <v>60.7</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>15.3</v>
+        <v>57.8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -6952,22 +7240,22 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -6977,78 +7265,102 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.8553</t>
+          <t>101.1264</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4894</t>
+          <t>0.4679</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.2122</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>70.51</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1986</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+          <t>0.1975</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -7114,7 +7426,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7122,11 +7434,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>53.3</v>
+        <v>48.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7140,65 +7464,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>38.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R5" t="n">
         <v>60.7</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U5" t="n">
         <v>54.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -7235,7 +7555,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -7308,15 +7628,39 @@
           <t>0.196</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7357,12 +7701,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7382,12 +7726,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7406,7 +7750,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52.1</v>
+        <v>46.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7420,11 +7764,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.8</v>
+        <v>42.5</v>
       </c>
       <c r="Q6" t="n">
         <v>15.3</v>
@@ -7433,49 +7777,45 @@
         <v>60.7</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>57.8</v>
+        <v>34.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7500,17 +7840,17 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -7525,67 +7865,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.1264</t>
+          <t>100.3793</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4679</t>
+          <t>0.3977</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2122</t>
+          <t>0.1805</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.3075</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.51</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>52.68</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.1907</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7620,7 +7960,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -7661,12 +8001,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7686,19 +8026,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>49.5</v>
+        <v>46.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7712,65 +8064,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>39.2</v>
+        <v>47</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R7" t="n">
         <v>60.7</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7787,12 +8135,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7802,12 +8150,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7817,78 +8165,102 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.5962</t>
+          <t>100.8553</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3663</t>
+          <t>0.4894</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1528</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.2866</t>
+          <t>0.371</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>74.08</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1678</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1986</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -7929,24 +8301,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>502671</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Paul Goldschmidt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -7954,19 +8326,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>48.3</v>
+        <v>44.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7980,65 +8364,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>33.8</v>
+        <v>39.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>15.3</v>
       </c>
       <c r="R8" t="n">
         <v>60.7</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8</v>
+        <v>18.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -8060,103 +8440,127 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 3/25, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>98.5765</t>
+          <t>99.7145</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1917</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>71.69</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1697</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+          <t>0.2004</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8197,12 +8601,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8222,19 +8626,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>47.8</v>
+        <v>44.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8248,65 +8664,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>45.5</v>
+        <v>57.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R9" t="n">
         <v>60.7</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -8323,27 +8735,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8353,78 +8765,102 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.0294</t>
+          <t>101.4308</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.4963</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.2478</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3265</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1622</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+          <t>0.234</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -8465,24 +8901,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -8490,19 +8926,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>45.8</v>
+        <v>44.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8516,65 +8964,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>43.9</v>
+        <v>30.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.2</v>
+        <v>15.3</v>
       </c>
       <c r="R10" t="n">
         <v>60.7</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>4.5</v>
+        <v>26.4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -8591,12 +9035,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -8606,12 +9050,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8621,78 +9065,102 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.5901</t>
+          <t>98.5451</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4091</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1732</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>32.13</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1879</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+          <t>0.1779</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -8733,24 +9201,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jazz Chisholm</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -8758,31 +9226,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>45.8</v>
+        <v>43.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8796,62 +9264,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>42.5</v>
+        <v>33.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="R11" t="n">
         <v>60.7</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U11" t="n">
-        <v>34.9</v>
+        <v>0.8</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8871,132 +9335,132 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>38.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.3793</t>
+          <t>98.5765</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3977</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1805</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3075</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>52.68</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1907</t>
+          <t>0.1697</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -9037,24 +9501,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>691176</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jasson Domínguez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -9062,19 +9526,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>45.6</v>
+        <v>43</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9088,65 +9564,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>33.3</v>
+        <v>28</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>15.2</v>
       </c>
       <c r="R12" t="n">
         <v>60.7</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>4.2</v>
+        <v>43.2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -9163,27 +9635,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 0 HR</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9193,78 +9665,102 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.9121</t>
+          <t>100.8327</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4172</t>
+          <t>0.3791</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1521</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3461</t>
+          <t>0.3046</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>74.17</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1497</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.1632</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -9305,24 +9801,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>641857</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -9330,31 +9826,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>45.3</v>
+        <v>42.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9368,62 +9864,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>49.9</v>
+        <v>45.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="R13" t="n">
         <v>60.7</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9443,27 +9935,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9473,102 +9965,102 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>102.1951</t>
+          <t>101.0294</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4113</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1807</t>
+          <t>0.1864</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3122</t>
+          <t>0.3265</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>74.49</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1677</t>
+          <t>0.1622</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -9609,12 +10101,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>669224</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9634,12 +10126,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9658,7 +10150,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.9</v>
+        <v>41.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9672,11 +10164,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>30.2</v>
+        <v>36.7</v>
       </c>
       <c r="Q14" t="n">
         <v>15.3</v>
@@ -9685,49 +10177,45 @@
         <v>60.7</v>
       </c>
       <c r="S14" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>26.4</v>
+        <v>41.2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9747,22 +10235,22 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -9777,67 +10265,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.5451</t>
+          <t>100.623</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.3675</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.2877</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>46.73</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1365</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -9872,7 +10360,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -9913,24 +10401,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>691176</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jasson Dominguez</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -9938,31 +10426,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>43.8</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9976,62 +10464,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>28</v>
+        <v>33.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.2</v>
+        <v>11.5</v>
       </c>
       <c r="R15" t="n">
         <v>60.7</v>
       </c>
       <c r="S15" t="n">
-        <v>92.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>43.2</v>
+        <v>4.2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10051,27 +10535,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -10081,102 +10565,102 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.8327</t>
+          <t>98.9121</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3791</t>
+          <t>0.4172</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.1521</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3046</t>
+          <t>0.3461</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>21.08</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>44.08</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1632</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10217,12 +10701,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10242,19 +10726,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>38.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10268,65 +10764,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>27.4</v>
+        <v>21.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>40.2</v>
+        <v>11.5</v>
       </c>
       <c r="R16" t="n">
         <v>60.7</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>36</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10343,12 +10835,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10358,12 +10850,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10373,78 +10865,102 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.14</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.1334</t>
+          <t>98.4444</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.3979</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1265</t>
+          <t>0.1209</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.3161</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.55</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.07</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1472</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+          <t>0.1315</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -10485,12 +11001,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680474</t>
+          <t>683011</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Max Schuemann</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10510,12 +11026,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10534,7 +11050,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.4</v>
+        <v>34.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10548,11 +11064,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>33</v>
+        <v>21.9</v>
       </c>
       <c r="Q17" t="n">
         <v>15.3</v>
@@ -10561,49 +11077,45 @@
         <v>60.7</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>22</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed; order MLB 5 vs RotoWire 9</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10628,7 +11140,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10638,7 +11150,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 4/15, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -10648,72 +11160,72 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.21</t>
+          <t>88.25</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.4682</t>
+          <t>98.8398</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3557</t>
+          <t>0.3427</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1411</t>
+          <t>0.1127</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2975</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.82</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1649</t>
+          <t>0.1097</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10748,7 +11260,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -10789,24 +11301,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>683011</t>
+          <t>672613</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Eliezer Alfonzo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -10814,31 +11326,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34</v>
+        <v>29.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10852,65 +11364,61 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>21.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.3</v>
+        <v>10.8</v>
       </c>
       <c r="R18" t="n">
         <v>60.7</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10922,17 +11430,17 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10942,117 +11450,117 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 0 HR</t>
+          <t>Last 5 games: 0/9, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.8398</t>
+          <t>95.0081</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3427</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1127</t>
+          <t>0.044</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2975</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1097</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -11093,12 +11601,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>645305</t>
+          <t>676609</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ali Sanchez</t>
+          <t>José Caballero</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -11118,7 +11626,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11142,7 +11650,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.2</v>
+        <v>26.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11156,11 +11664,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q19" t="n">
         <v>15.3</v>
@@ -11169,49 +11677,45 @@
         <v>60.7</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>9.300000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11231,12 +11735,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -11246,7 +11750,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/11, 0 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -11261,67 +11765,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.46</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>95.6331</t>
+          <t>96.3508</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.3306</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0847</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2776</t>
+          <t>0.2794</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>68.96</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0702</t>
+          <t>0.1348</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -11356,7 +11860,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-07-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-19.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>11.5</v>
       </c>
       <c r="R2" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S2" t="n">
         <v>93.2</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1027,19 +1027,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1080,7 +1072,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1104,7 +1096,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.3</v>
+        <v>60.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1128,7 +1120,7 @@
         <v>15.3</v>
       </c>
       <c r="R3" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -1319,7 +1311,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1327,19 +1319,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1380,7 +1364,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1404,7 +1388,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.7</v>
+        <v>53.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1428,7 +1412,7 @@
         <v>15.3</v>
       </c>
       <c r="R4" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -1619,7 +1603,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1627,19 +1611,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -1680,7 +1656,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1704,7 +1680,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.4</v>
+        <v>49</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1728,7 +1704,7 @@
         <v>11.5</v>
       </c>
       <c r="R5" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1919,7 +1895,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1927,19 +1903,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -1980,7 +1948,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2004,7 +1972,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.4</v>
+        <v>46.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2028,7 +1996,7 @@
         <v>15.3</v>
       </c>
       <c r="R6" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -2219,7 +2187,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2227,19 +2195,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2280,7 +2240,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2304,7 +2264,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.2</v>
+        <v>46.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2328,7 +2288,7 @@
         <v>11.5</v>
       </c>
       <c r="R7" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2519,7 +2479,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2527,19 +2487,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -2580,7 +2532,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2604,7 +2556,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.6</v>
+        <v>45.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2628,7 +2580,7 @@
         <v>15.3</v>
       </c>
       <c r="R8" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -2819,7 +2771,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2827,19 +2779,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -2855,24 +2799,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -2880,31 +2824,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Ryan Yarbrough</t>
+          <t>Will Klein</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>642232</t>
+          <t>694361</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.5</v>
+        <v>45.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2918,26 +2862,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>57.3</v>
+        <v>30.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.5</v>
+        <v>15.3</v>
       </c>
       <c r="R9" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S9" t="n">
-        <v>52.4</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>37.8</v>
+        <v>26.4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2951,7 +2895,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2989,27 +2933,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -3019,97 +2963,97 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.46</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.4308</t>
+          <t>98.5451</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4963</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2478</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>34.88</t>
+          <t>32.13</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>84.49</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3394</t>
+          <t>0.3158</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1149</t>
+          <t>0.0838</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -3119,7 +3063,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3127,19 +3071,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -3155,24 +3091,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -3180,31 +3116,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3218,26 +3154,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>30.2</v>
+        <v>57.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="R10" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S10" t="n">
-        <v>94.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>26.4</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3251,7 +3187,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3289,27 +3225,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3319,97 +3255,97 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.5451</t>
+          <t>101.4308</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.4963</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.2478</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.234</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -3419,7 +3355,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3427,19 +3363,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -3480,7 +3408,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3504,7 +3432,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.4</v>
+        <v>43.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3528,7 +3456,7 @@
         <v>11.5</v>
       </c>
       <c r="R11" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -3719,7 +3647,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3727,19 +3655,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -3780,7 +3700,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3804,7 +3724,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3828,7 +3748,7 @@
         <v>15.2</v>
       </c>
       <c r="R12" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -4019,7 +3939,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -4027,19 +3947,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -4080,7 +3992,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4104,7 +4016,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>42.9</v>
+        <v>43.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4128,7 +4040,7 @@
         <v>11.5</v>
       </c>
       <c r="R13" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S13" t="n">
         <v>64.3</v>
@@ -4319,7 +4231,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4327,19 +4239,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -4380,7 +4284,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4404,7 +4308,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4428,7 +4332,7 @@
         <v>15.3</v>
       </c>
       <c r="R14" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -4619,7 +4523,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4627,19 +4531,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -4680,7 +4576,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4704,7 +4600,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4728,7 +4624,7 @@
         <v>11.5</v>
       </c>
       <c r="R15" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S15" t="n">
         <v>86.40000000000001</v>
@@ -4919,7 +4815,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4927,19 +4823,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -4980,7 +4868,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5004,7 +4892,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5028,7 +4916,7 @@
         <v>11.5</v>
       </c>
       <c r="R16" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S16" t="n">
         <v>76.2</v>
@@ -5219,7 +5107,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -5227,19 +5115,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -5280,7 +5160,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5304,7 +5184,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34.6</v>
+        <v>35.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5328,7 +5208,7 @@
         <v>15.3</v>
       </c>
       <c r="R17" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -5519,7 +5399,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5527,19 +5407,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -5580,7 +5452,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5604,7 +5476,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.1</v>
+        <v>29.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5628,7 +5500,7 @@
         <v>10.8</v>
       </c>
       <c r="R18" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -5819,7 +5691,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5827,19 +5699,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -5880,7 +5744,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5904,7 +5768,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.9</v>
+        <v>27.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5928,7 +5792,7 @@
         <v>15.3</v>
       </c>
       <c r="R19" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -6119,7 +5983,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6127,19 +5991,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -6526,7 +6382,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6550,7 +6406,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6574,7 +6430,7 @@
         <v>11.5</v>
       </c>
       <c r="R2" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S2" t="n">
         <v>93.2</v>
@@ -6765,7 +6621,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6773,19 +6629,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -6826,7 +6674,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6850,7 +6698,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.3</v>
+        <v>60.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6874,7 +6722,7 @@
         <v>15.3</v>
       </c>
       <c r="R3" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -7065,7 +6913,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -7073,19 +6921,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -7126,7 +6966,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7150,7 +6990,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.7</v>
+        <v>53.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7174,7 +7014,7 @@
         <v>15.3</v>
       </c>
       <c r="R4" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -7365,7 +7205,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -7373,19 +7213,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -7426,7 +7258,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7450,7 +7282,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.4</v>
+        <v>49</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7474,7 +7306,7 @@
         <v>11.5</v>
       </c>
       <c r="R5" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7665,7 +7497,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7673,19 +7505,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -7726,7 +7550,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7750,7 +7574,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.4</v>
+        <v>46.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7774,7 +7598,7 @@
         <v>15.3</v>
       </c>
       <c r="R6" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -7965,7 +7789,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7973,19 +7797,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -8026,7 +7842,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8050,7 +7866,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.2</v>
+        <v>46.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8074,7 +7890,7 @@
         <v>11.5</v>
       </c>
       <c r="R7" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -8265,7 +8081,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -8273,19 +8089,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -8326,7 +8134,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8350,7 +8158,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.6</v>
+        <v>45.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8374,7 +8182,7 @@
         <v>15.3</v>
       </c>
       <c r="R8" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -8565,7 +8373,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8573,19 +8381,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -8601,24 +8401,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -8626,31 +8426,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Ryan Yarbrough</t>
+          <t>Will Klein</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>642232</t>
+          <t>694361</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.5</v>
+        <v>45.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8664,26 +8464,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>57.3</v>
+        <v>30.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.5</v>
+        <v>15.3</v>
       </c>
       <c r="R9" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S9" t="n">
-        <v>52.4</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>37.8</v>
+        <v>26.4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -8697,7 +8497,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -8735,27 +8535,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8765,97 +8565,97 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.46</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.4308</t>
+          <t>98.5451</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4963</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2478</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>34.88</t>
+          <t>32.13</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>84.49</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3394</t>
+          <t>0.3158</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1149</t>
+          <t>0.0838</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -8865,7 +8665,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8873,19 +8673,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -8901,24 +8693,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -8926,31 +8718,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8964,26 +8756,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>30.2</v>
+        <v>57.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="R10" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S10" t="n">
-        <v>94.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>26.4</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8997,7 +8789,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -9035,27 +8827,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -9065,97 +8857,97 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.5451</t>
+          <t>101.4308</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.4963</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.2478</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.234</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -9165,7 +8957,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -9173,19 +8965,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -9226,7 +9010,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9250,7 +9034,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.4</v>
+        <v>43.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9274,7 +9058,7 @@
         <v>11.5</v>
       </c>
       <c r="R11" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -9465,7 +9249,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -9473,19 +9257,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -9526,7 +9302,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9550,7 +9326,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9574,7 +9350,7 @@
         <v>15.2</v>
       </c>
       <c r="R12" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -9765,7 +9541,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9773,19 +9549,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -9826,7 +9594,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9850,7 +9618,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>42.9</v>
+        <v>43.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9874,7 +9642,7 @@
         <v>11.5</v>
       </c>
       <c r="R13" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S13" t="n">
         <v>64.3</v>
@@ -10065,7 +9833,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -10073,19 +9841,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -10126,7 +9886,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10150,7 +9910,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10174,7 +9934,7 @@
         <v>15.3</v>
       </c>
       <c r="R14" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -10365,7 +10125,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -10373,19 +10133,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -10426,7 +10178,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10450,7 +10202,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10474,7 +10226,7 @@
         <v>11.5</v>
       </c>
       <c r="R15" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S15" t="n">
         <v>86.40000000000001</v>
@@ -10665,7 +10417,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10673,19 +10425,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -10726,7 +10470,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10750,7 +10494,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10774,7 +10518,7 @@
         <v>11.5</v>
       </c>
       <c r="R16" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S16" t="n">
         <v>76.2</v>
@@ -10965,7 +10709,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10973,19 +10717,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -11026,7 +10762,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11050,7 +10786,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34.6</v>
+        <v>35.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11074,7 +10810,7 @@
         <v>15.3</v>
       </c>
       <c r="R17" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -11265,7 +11001,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -11273,19 +11009,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -11326,7 +11054,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11350,7 +11078,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.1</v>
+        <v>29.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11374,7 +11102,7 @@
         <v>10.8</v>
       </c>
       <c r="R18" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -11565,7 +11293,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -11573,19 +11301,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -11626,7 +11346,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11650,7 +11370,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.9</v>
+        <v>27.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11674,7 +11394,7 @@
         <v>15.3</v>
       </c>
       <c r="R19" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11865,7 +11585,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -11873,19 +11593,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
